--- a/data/template/报价系统功能基础数据功能结构所需字段——rockwell.xlsx
+++ b/data/template/报价系统功能基础数据功能结构所需字段——rockwell.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\a-joii\project\CPQ-superpowers-v2\CPQ-superpowers\dev\data\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEDAD45C-89B9-4245-B26B-D080C82F7AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{850196D7-EAC6-434F-A465-F6CA305B07AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="912" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="912" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="元素单价" sheetId="1" r:id="rId1"/>
@@ -37,6 +37,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">成品其他费用!$A$1:$G$85</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">来料BOM!$A$1:$N$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">来料固定加工费!$A$1:$M$127</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">元素BOM!$A$1:$K$141</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">组装加工费!$A$1:$G$114</definedName>
   </definedNames>
@@ -82,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4075" uniqueCount="694">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4062" uniqueCount="694">
   <si>
     <t>客户编号</t>
   </si>
@@ -9637,8 +9638,8 @@
       <c r="C5" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>46</v>
+      <c r="D5" s="5">
+        <v>4170010173</v>
       </c>
       <c r="G5" s="39" t="s">
         <v>40</v>
@@ -9926,8 +9927,8 @@
       <c r="C22" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>73</v>
+      <c r="D22" s="5">
+        <v>3120014707</v>
       </c>
       <c r="G22" s="39" t="s">
         <v>40</v>
@@ -14814,8 +14815,8 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
-        <v>39</v>
+      <c r="A2" s="5">
+        <v>3120014696</v>
       </c>
       <c r="B2" s="27">
         <v>1</v>
@@ -14825,8 +14826,8 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>39</v>
+      <c r="A3" s="5">
+        <v>3120014696</v>
       </c>
       <c r="B3" s="27">
         <v>3</v>
@@ -14836,8 +14837,8 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>42</v>
+      <c r="A4" s="5">
+        <v>3100280217</v>
       </c>
       <c r="B4" s="27">
         <v>1</v>
@@ -14847,8 +14848,8 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
-        <v>42</v>
+      <c r="A5" s="5">
+        <v>3100280217</v>
       </c>
       <c r="B5" s="27">
         <v>3</v>
@@ -14858,8 +14859,8 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
-        <v>44</v>
+      <c r="A6" s="5">
+        <v>3120014699</v>
       </c>
       <c r="B6" s="27">
         <v>1</v>
@@ -14869,8 +14870,8 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
-        <v>44</v>
+      <c r="A7" s="5">
+        <v>3120014699</v>
       </c>
       <c r="B7" s="27">
         <v>3</v>
@@ -14880,8 +14881,8 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>46</v>
+      <c r="A8" s="5">
+        <v>4170010173</v>
       </c>
       <c r="B8" s="27">
         <v>1</v>
@@ -14891,8 +14892,8 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
-        <v>46</v>
+      <c r="A9" s="5">
+        <v>4170010173</v>
       </c>
       <c r="B9" s="27">
         <v>3</v>
@@ -14902,8 +14903,8 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>47</v>
+      <c r="A10" s="5">
+        <v>3120014695</v>
       </c>
       <c r="B10" s="27">
         <v>1</v>
@@ -14913,8 +14914,8 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>47</v>
+      <c r="A11" s="5">
+        <v>3120014695</v>
       </c>
       <c r="B11" s="27">
         <v>3</v>
@@ -14924,8 +14925,8 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
-        <v>48</v>
+      <c r="A12" s="5">
+        <v>4140010115</v>
       </c>
       <c r="B12" s="27">
         <v>1</v>
@@ -18961,6 +18962,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:M127"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -19019,7 +19021,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>39</v>
       </c>
@@ -19042,7 +19044,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>39</v>
       </c>
@@ -19065,7 +19067,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>42</v>
       </c>
@@ -19088,7 +19090,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>42</v>
       </c>
@@ -19111,7 +19113,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>44</v>
       </c>
@@ -19134,7 +19136,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>44</v>
       </c>
@@ -19157,7 +19159,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>46</v>
       </c>
@@ -19180,7 +19182,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>46</v>
       </c>
@@ -19203,7 +19205,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>47</v>
       </c>
@@ -19226,7 +19228,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>47</v>
       </c>
@@ -19249,7 +19251,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>48</v>
       </c>
@@ -19272,7 +19274,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>48</v>
       </c>
@@ -19295,7 +19297,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>50</v>
       </c>
@@ -19318,7 +19320,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>50</v>
       </c>
@@ -19341,7 +19343,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>51</v>
       </c>
@@ -19364,7 +19366,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>51</v>
       </c>
@@ -19387,7 +19389,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>52</v>
       </c>
@@ -19410,7 +19412,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>52</v>
       </c>
@@ -19433,7 +19435,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>54</v>
       </c>
@@ -19456,7 +19458,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>54</v>
       </c>
@@ -19479,7 +19481,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>55</v>
       </c>
@@ -19502,7 +19504,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>55</v>
       </c>
@@ -19525,7 +19527,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>57</v>
       </c>
@@ -19548,7 +19550,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
         <v>57</v>
       </c>
@@ -19571,7 +19573,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>58</v>
       </c>
@@ -19594,7 +19596,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
         <v>58</v>
       </c>
@@ -19617,7 +19619,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
         <v>60</v>
       </c>
@@ -19640,7 +19642,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>60</v>
       </c>
@@ -19663,7 +19665,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
         <v>62</v>
       </c>
@@ -19686,7 +19688,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>62</v>
       </c>
@@ -19709,7 +19711,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>63</v>
       </c>
@@ -19732,7 +19734,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>63</v>
       </c>
@@ -19755,7 +19757,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
         <v>65</v>
       </c>
@@ -19778,7 +19780,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
         <v>65</v>
       </c>
@@ -19801,7 +19803,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
         <v>67</v>
       </c>
@@ -19824,7 +19826,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
         <v>67</v>
       </c>
@@ -19847,7 +19849,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
         <v>69</v>
       </c>
@@ -19870,7 +19872,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
         <v>69</v>
       </c>
@@ -19893,7 +19895,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
         <v>71</v>
       </c>
@@ -19916,7 +19918,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
         <v>71</v>
       </c>
@@ -19939,7 +19941,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
         <v>73</v>
       </c>
@@ -19962,7 +19964,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
         <v>73</v>
       </c>
@@ -19985,7 +19987,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
         <v>189</v>
       </c>
@@ -20008,7 +20010,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
         <v>189</v>
       </c>
@@ -20031,7 +20033,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
         <v>193</v>
       </c>
@@ -20054,7 +20056,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
         <v>193</v>
       </c>
@@ -20077,7 +20079,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
         <v>195</v>
       </c>
@@ -20100,7 +20102,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
         <v>195</v>
       </c>
@@ -20123,7 +20125,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
         <v>197</v>
       </c>
@@ -20146,7 +20148,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
         <v>197</v>
       </c>
@@ -20169,7 +20171,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
         <v>199</v>
       </c>
@@ -20192,7 +20194,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
         <v>199</v>
       </c>
@@ -20215,7 +20217,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
         <v>75</v>
       </c>
@@ -20238,7 +20240,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
         <v>75</v>
       </c>
@@ -20261,7 +20263,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="5" t="s">
         <v>77</v>
       </c>
@@ -20284,7 +20286,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
         <v>77</v>
       </c>
@@ -20307,7 +20309,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
         <v>79</v>
       </c>
@@ -20330,7 +20332,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
         <v>79</v>
       </c>
@@ -20353,7 +20355,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
         <v>81</v>
       </c>
@@ -20376,7 +20378,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" s="5" t="s">
         <v>81</v>
       </c>
@@ -20399,7 +20401,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
         <v>83</v>
       </c>
@@ -20422,7 +20424,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" s="5" t="s">
         <v>83</v>
       </c>
@@ -20445,7 +20447,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
         <v>85</v>
       </c>
@@ -20468,7 +20470,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
         <v>85</v>
       </c>
@@ -20491,7 +20493,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
         <v>201</v>
       </c>
@@ -20514,7 +20516,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
         <v>201</v>
       </c>
@@ -20537,7 +20539,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
         <v>203</v>
       </c>
@@ -20560,7 +20562,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
         <v>203</v>
       </c>
@@ -20583,7 +20585,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
         <v>205</v>
       </c>
@@ -20606,7 +20608,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" s="5" t="s">
         <v>205</v>
       </c>
@@ -20629,7 +20631,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" s="5" t="s">
         <v>117</v>
       </c>
@@ -20652,7 +20654,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" s="5" t="s">
         <v>117</v>
       </c>
@@ -20675,7 +20677,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
         <v>117</v>
       </c>
@@ -20698,7 +20700,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
         <v>119</v>
       </c>
@@ -20721,7 +20723,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
         <v>119</v>
       </c>
@@ -20744,7 +20746,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
         <v>119</v>
       </c>
@@ -20767,7 +20769,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
         <v>121</v>
       </c>
@@ -20790,7 +20792,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
         <v>121</v>
       </c>
@@ -20813,7 +20815,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
         <v>122</v>
       </c>
@@ -20836,7 +20838,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
         <v>122</v>
       </c>
@@ -20859,7 +20861,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
         <v>124</v>
       </c>
@@ -20882,7 +20884,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="s">
         <v>124</v>
       </c>
@@ -20905,7 +20907,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" s="5" t="s">
         <v>125</v>
       </c>
@@ -20928,7 +20930,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
         <v>125</v>
       </c>
@@ -20951,7 +20953,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" s="5" t="s">
         <v>127</v>
       </c>
@@ -20974,7 +20976,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" s="5" t="s">
         <v>127</v>
       </c>
@@ -20997,7 +20999,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" s="5" t="s">
         <v>129</v>
       </c>
@@ -21020,7 +21022,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="s">
         <v>129</v>
       </c>
@@ -21043,7 +21045,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="s">
         <v>131</v>
       </c>
@@ -21066,7 +21068,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" s="5" t="s">
         <v>131</v>
       </c>
@@ -21089,7 +21091,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" s="5" t="s">
         <v>133</v>
       </c>
@@ -21112,7 +21114,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" s="5" t="s">
         <v>133</v>
       </c>
@@ -21135,7 +21137,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" s="5" t="s">
         <v>135</v>
       </c>
@@ -21158,7 +21160,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" s="5" t="s">
         <v>135</v>
       </c>
@@ -21181,7 +21183,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" s="5" t="s">
         <v>137</v>
       </c>
@@ -21204,7 +21206,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" s="5" t="s">
         <v>137</v>
       </c>
@@ -21227,7 +21229,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" s="5" t="s">
         <v>139</v>
       </c>
@@ -21250,7 +21252,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" s="5" t="s">
         <v>139</v>
       </c>
@@ -21273,7 +21275,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" s="5" t="s">
         <v>141</v>
       </c>
@@ -21296,7 +21298,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" s="5" t="s">
         <v>141</v>
       </c>
@@ -21319,7 +21321,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" s="5" t="s">
         <v>143</v>
       </c>
@@ -21342,7 +21344,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" s="5" t="s">
         <v>143</v>
       </c>
@@ -21365,7 +21367,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" s="5" t="s">
         <v>145</v>
       </c>
@@ -21388,7 +21390,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" s="5" t="s">
         <v>145</v>
       </c>
@@ -21411,7 +21413,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" s="5" t="s">
         <v>147</v>
       </c>
@@ -21434,7 +21436,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" s="5" t="s">
         <v>147</v>
       </c>
@@ -21457,7 +21459,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" s="5" t="s">
         <v>149</v>
       </c>
@@ -21480,7 +21482,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" s="5" t="s">
         <v>149</v>
       </c>
@@ -21503,7 +21505,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" s="5" t="s">
         <v>151</v>
       </c>
@@ -21526,7 +21528,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" s="5" t="s">
         <v>151</v>
       </c>
@@ -21549,7 +21551,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" s="5" t="s">
         <v>153</v>
       </c>
@@ -21572,7 +21574,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" s="5" t="s">
         <v>153</v>
       </c>
@@ -21595,7 +21597,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" s="5" t="s">
         <v>155</v>
       </c>
@@ -21618,7 +21620,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" s="5" t="s">
         <v>157</v>
       </c>
@@ -21641,7 +21643,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" s="5" t="s">
         <v>157</v>
       </c>
@@ -21664,7 +21666,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" s="5" t="s">
         <v>159</v>
       </c>
@@ -21687,7 +21689,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" s="5" t="s">
         <v>159</v>
       </c>
@@ -21710,7 +21712,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" s="5" t="s">
         <v>161</v>
       </c>
@@ -21733,7 +21735,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" s="5" t="s">
         <v>161</v>
       </c>
@@ -21802,7 +21804,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
         <v>164</v>
       </c>
@@ -21825,7 +21827,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" s="5" t="s">
         <v>164</v>
       </c>
@@ -21848,7 +21850,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" s="5" t="s">
         <v>166</v>
       </c>
@@ -21871,7 +21873,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" s="5" t="s">
         <v>170</v>
       </c>
@@ -21894,7 +21896,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" s="5" t="s">
         <v>170</v>
       </c>
@@ -21918,6 +21920,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M127" xr:uid="{00000000-0001-0000-0500-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="3100070021"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="150" verticalDpi="150"/>

--- a/data/template/报价系统功能基础数据功能结构所需字段——rockwell.xlsx
+++ b/data/template/报价系统功能基础数据功能结构所需字段——rockwell.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\a-joii\project\CPQ-superpowers-v2\CPQ-superpowers\dev\data\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\a-joii\project\CPQ-superpowers-v2\dev\data\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{850196D7-EAC6-434F-A465-F6CA305B07AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AA491D7-D008-4F98-B658-B7D45D6B6850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="912" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,21 +25,23 @@
     <sheet name="成品固定加工费" sheetId="4" state="hidden" r:id="rId10"/>
     <sheet name="成品其他费用" sheetId="19" r:id="rId11"/>
     <sheet name="组成件BOM" sheetId="5" r:id="rId12"/>
-    <sheet name="组成件其他费用" sheetId="23" r:id="rId13"/>
-    <sheet name="组装加工费" sheetId="11" r:id="rId14"/>
-    <sheet name="汇总" sheetId="24" r:id="rId15"/>
-    <sheet name="组装加工费年降" sheetId="20" state="hidden" r:id="rId16"/>
-    <sheet name="电镀方案" sheetId="7" state="hidden" r:id="rId17"/>
-    <sheet name="电镀费用" sheetId="8" state="hidden" r:id="rId18"/>
-    <sheet name="单重" sheetId="9" state="hidden" r:id="rId19"/>
-    <sheet name="年降系数" sheetId="16" state="hidden" r:id="rId20"/>
+    <sheet name="Sheet1" sheetId="25" r:id="rId13"/>
+    <sheet name="组成件其他费用" sheetId="23" r:id="rId14"/>
+    <sheet name="组装加工费" sheetId="11" r:id="rId15"/>
+    <sheet name="汇总" sheetId="24" r:id="rId16"/>
+    <sheet name="组装加工费年降" sheetId="20" state="hidden" r:id="rId17"/>
+    <sheet name="电镀方案" sheetId="7" state="hidden" r:id="rId18"/>
+    <sheet name="电镀费用" sheetId="8" state="hidden" r:id="rId19"/>
+    <sheet name="单重" sheetId="9" state="hidden" r:id="rId20"/>
+    <sheet name="年降系数" sheetId="16" state="hidden" r:id="rId21"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">成品其他费用!$A$1:$G$85</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">来料BOM!$A$1:$N$75</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">来料固定加工费!$A$1:$M$127</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">元素BOM!$A$1:$K$141</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">组装加工费!$A$1:$G$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">组成件BOM!$A$1:$L$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">组装加工费!$A$1:$G$114</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -83,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4062" uniqueCount="694">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4171" uniqueCount="694">
   <si>
     <t>客户编号</t>
   </si>
@@ -983,9 +985,6 @@
   </si>
   <si>
     <t>焊接费用</t>
-  </si>
-  <si>
-    <t>RMB/PCS</t>
   </si>
   <si>
     <t>二次处理费</t>
@@ -2249,7 +2248,11 @@
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
-    <t>RMB/PCS</t>
+    <t>RMB</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>PCS</t>
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
 </sst>
@@ -2262,7 +2265,7 @@
     <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2390,6 +2393,12 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1976D2"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -2485,7 +2494,7 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2599,6 +2608,7 @@
     <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4984,6 +4994,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:L79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -5027,8 +5038,8 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
-        <v>117</v>
+      <c r="A2" s="5">
+        <v>3120015693</v>
       </c>
       <c r="D2" s="27" t="s">
         <v>292</v>
@@ -5046,7 +5057,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>119</v>
       </c>
@@ -5066,7 +5077,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <v>3120014696</v>
       </c>
@@ -5077,7 +5088,7 @@
         <v>2</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="27">
@@ -5090,7 +5101,7 @@
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>39</v>
       </c>
@@ -5114,7 +5125,7 @@
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>42</v>
       </c>
@@ -5138,7 +5149,7 @@
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>42</v>
       </c>
@@ -5162,7 +5173,7 @@
       <c r="K7" s="5"/>
       <c r="L7" s="5"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>44</v>
       </c>
@@ -5186,7 +5197,7 @@
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>44</v>
       </c>
@@ -5210,7 +5221,7 @@
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>46</v>
       </c>
@@ -5234,7 +5245,7 @@
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>46</v>
       </c>
@@ -5258,7 +5269,7 @@
       <c r="K11" s="5"/>
       <c r="L11" s="5"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>47</v>
       </c>
@@ -5282,7 +5293,7 @@
       <c r="K12" s="5"/>
       <c r="L12" s="5"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>47</v>
       </c>
@@ -5306,7 +5317,7 @@
       <c r="K13" s="5"/>
       <c r="L13" s="5"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>48</v>
       </c>
@@ -5330,7 +5341,7 @@
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>48</v>
       </c>
@@ -5354,7 +5365,7 @@
       <c r="K15" s="5"/>
       <c r="L15" s="5"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>50</v>
       </c>
@@ -5378,7 +5389,7 @@
       <c r="K16" s="5"/>
       <c r="L16" s="5"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>50</v>
       </c>
@@ -5402,7 +5413,7 @@
       <c r="K17" s="5"/>
       <c r="L17" s="5"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>51</v>
       </c>
@@ -5426,7 +5437,7 @@
       <c r="K18" s="5"/>
       <c r="L18" s="5"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>51</v>
       </c>
@@ -5450,7 +5461,7 @@
       <c r="K19" s="5"/>
       <c r="L19" s="5"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>52</v>
       </c>
@@ -5474,7 +5485,7 @@
       <c r="K20" s="5"/>
       <c r="L20" s="5"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>52</v>
       </c>
@@ -5498,7 +5509,7 @@
       <c r="K21" s="5"/>
       <c r="L21" s="5"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>54</v>
       </c>
@@ -5522,7 +5533,7 @@
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>54</v>
       </c>
@@ -5546,7 +5557,7 @@
       <c r="K23" s="5"/>
       <c r="L23" s="5"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>55</v>
       </c>
@@ -5570,7 +5581,7 @@
       <c r="K24" s="5"/>
       <c r="L24" s="5"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
         <v>55</v>
       </c>
@@ -5594,7 +5605,7 @@
       <c r="K25" s="5"/>
       <c r="L25" s="5"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>57</v>
       </c>
@@ -5618,7 +5629,7 @@
       <c r="K26" s="5"/>
       <c r="L26" s="5"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
         <v>57</v>
       </c>
@@ -5642,7 +5653,7 @@
       <c r="K27" s="5"/>
       <c r="L27" s="5"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
         <v>58</v>
       </c>
@@ -5666,7 +5677,7 @@
       <c r="K28" s="5"/>
       <c r="L28" s="5"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>58</v>
       </c>
@@ -5690,7 +5701,7 @@
       <c r="K29" s="5"/>
       <c r="L29" s="5"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
         <v>60</v>
       </c>
@@ -5714,7 +5725,7 @@
       <c r="K30" s="5"/>
       <c r="L30" s="5"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>60</v>
       </c>
@@ -5738,7 +5749,7 @@
       <c r="K31" s="5"/>
       <c r="L31" s="5"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>62</v>
       </c>
@@ -5762,7 +5773,7 @@
       <c r="K32" s="5"/>
       <c r="L32" s="5"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>62</v>
       </c>
@@ -5786,7 +5797,7 @@
       <c r="K33" s="5"/>
       <c r="L33" s="5"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
         <v>63</v>
       </c>
@@ -5810,7 +5821,7 @@
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
         <v>63</v>
       </c>
@@ -5834,7 +5845,7 @@
       <c r="K35" s="5"/>
       <c r="L35" s="5"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
         <v>65</v>
       </c>
@@ -5858,7 +5869,7 @@
       <c r="K36" s="5"/>
       <c r="L36" s="5"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
         <v>65</v>
       </c>
@@ -5882,7 +5893,7 @@
       <c r="K37" s="5"/>
       <c r="L37" s="5"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
         <v>67</v>
       </c>
@@ -5906,7 +5917,7 @@
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
         <v>67</v>
       </c>
@@ -5930,7 +5941,7 @@
       <c r="K39" s="5"/>
       <c r="L39" s="5"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
         <v>69</v>
       </c>
@@ -5954,7 +5965,7 @@
       <c r="K40" s="5"/>
       <c r="L40" s="5"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
         <v>69</v>
       </c>
@@ -5978,7 +5989,7 @@
       <c r="K41" s="5"/>
       <c r="L41" s="5"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
         <v>71</v>
       </c>
@@ -6002,7 +6013,7 @@
       <c r="K42" s="5"/>
       <c r="L42" s="5"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
         <v>71</v>
       </c>
@@ -6026,7 +6037,7 @@
       <c r="K43" s="5"/>
       <c r="L43" s="5"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
         <v>73</v>
       </c>
@@ -6050,7 +6061,7 @@
       <c r="K44" s="5"/>
       <c r="L44" s="5"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
         <v>73</v>
       </c>
@@ -6074,7 +6085,7 @@
       <c r="K45" s="5"/>
       <c r="L45" s="5"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
         <v>189</v>
       </c>
@@ -6098,7 +6109,7 @@
       <c r="K46" s="5"/>
       <c r="L46" s="5"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
         <v>189</v>
       </c>
@@ -6122,7 +6133,7 @@
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
         <v>193</v>
       </c>
@@ -6146,7 +6157,7 @@
       <c r="K48" s="5"/>
       <c r="L48" s="5"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
         <v>193</v>
       </c>
@@ -6170,7 +6181,7 @@
       <c r="K49" s="5"/>
       <c r="L49" s="5"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
         <v>195</v>
       </c>
@@ -6194,7 +6205,7 @@
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
         <v>195</v>
       </c>
@@ -6218,7 +6229,7 @@
       <c r="K51" s="5"/>
       <c r="L51" s="5"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
         <v>197</v>
       </c>
@@ -6242,7 +6253,7 @@
       <c r="K52" s="5"/>
       <c r="L52" s="5"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
         <v>197</v>
       </c>
@@ -6266,7 +6277,7 @@
       <c r="K53" s="5"/>
       <c r="L53" s="5"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
         <v>199</v>
       </c>
@@ -6290,7 +6301,7 @@
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
         <v>199</v>
       </c>
@@ -6314,7 +6325,7 @@
       <c r="K55" s="5"/>
       <c r="L55" s="5"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="5" t="s">
         <v>75</v>
       </c>
@@ -6338,7 +6349,7 @@
       <c r="K56" s="5"/>
       <c r="L56" s="5"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
         <v>75</v>
       </c>
@@ -6362,7 +6373,7 @@
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
         <v>77</v>
       </c>
@@ -6386,7 +6397,7 @@
       <c r="K58" s="5"/>
       <c r="L58" s="5"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
         <v>77</v>
       </c>
@@ -6410,7 +6421,7 @@
       <c r="K59" s="5"/>
       <c r="L59" s="5"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
         <v>79</v>
       </c>
@@ -6434,7 +6445,7 @@
       <c r="K60" s="5"/>
       <c r="L60" s="5"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" s="5" t="s">
         <v>79</v>
       </c>
@@ -6458,7 +6469,7 @@
       <c r="K61" s="5"/>
       <c r="L61" s="5"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
         <v>81</v>
       </c>
@@ -6482,7 +6493,7 @@
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" s="5" t="s">
         <v>81</v>
       </c>
@@ -6506,7 +6517,7 @@
       <c r="K63" s="5"/>
       <c r="L63" s="5"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
         <v>83</v>
       </c>
@@ -6530,7 +6541,7 @@
       <c r="K64" s="5"/>
       <c r="L64" s="5"/>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
         <v>83</v>
       </c>
@@ -6554,7 +6565,7 @@
       <c r="K65" s="5"/>
       <c r="L65" s="5"/>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
         <v>85</v>
       </c>
@@ -6578,7 +6589,7 @@
       <c r="K66" s="5"/>
       <c r="L66" s="5"/>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
         <v>85</v>
       </c>
@@ -6602,7 +6613,7 @@
       <c r="K67" s="5"/>
       <c r="L67" s="5"/>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
         <v>201</v>
       </c>
@@ -6626,7 +6637,7 @@
       <c r="K68" s="5"/>
       <c r="L68" s="5"/>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
         <v>201</v>
       </c>
@@ -6650,7 +6661,7 @@
       <c r="K69" s="5"/>
       <c r="L69" s="5"/>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
         <v>203</v>
       </c>
@@ -6674,7 +6685,7 @@
       <c r="K70" s="5"/>
       <c r="L70" s="5"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" s="5" t="s">
         <v>203</v>
       </c>
@@ -6698,7 +6709,7 @@
       <c r="K71" s="5"/>
       <c r="L71" s="5"/>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" s="5" t="s">
         <v>205</v>
       </c>
@@ -6722,7 +6733,7 @@
       <c r="K72" s="5"/>
       <c r="L72" s="5"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" s="5" t="s">
         <v>205</v>
       </c>
@@ -6818,7 +6829,7 @@
       <c r="K76" s="5"/>
       <c r="L76" s="5"/>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
         <v>119</v>
       </c>
@@ -6842,7 +6853,7 @@
       <c r="K77" s="5"/>
       <c r="L77" s="5"/>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
         <v>119</v>
       </c>
@@ -6866,7 +6877,7 @@
       <c r="K78" s="5"/>
       <c r="L78" s="5"/>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
         <v>119</v>
       </c>
@@ -6889,6 +6900,33 @@
       <c r="J79" s="5"/>
       <c r="K79" s="5"/>
       <c r="L79" s="5"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L79" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="3120015693"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <phoneticPr fontId="16" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62025654-4641-4781-B5C1-A16BA1A10F1F}">
+  <dimension ref="G18:H18"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="18" spans="7:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="G18" s="45">
+        <v>1.090125</v>
+      </c>
+      <c r="H18">
+        <f>G18/1000</f>
+        <v>1.0901249999999999E-3</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="16" type="noConversion"/>
@@ -6896,7 +6934,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:O3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -7029,7 +7067,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:G114"/>
   <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -7079,6 +7117,9 @@
         <v>0.1</v>
       </c>
       <c r="E2" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F2" s="32" t="s">
         <v>693</v>
       </c>
     </row>
@@ -7095,8 +7136,11 @@
       <c r="D3" s="5">
         <v>0.1</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>300</v>
+      <c r="E3" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -7112,8 +7156,11 @@
       <c r="D4" s="5">
         <v>0.1</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>300</v>
+      <c r="E4" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -7129,8 +7176,11 @@
       <c r="D5" s="5">
         <v>0.1</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>300</v>
+      <c r="E5" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F5" s="32" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -7146,8 +7196,11 @@
       <c r="D6" s="5">
         <v>0.1</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>300</v>
+      <c r="E6" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F6" s="32" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -7163,8 +7216,11 @@
       <c r="D7" s="5">
         <v>0.1</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>300</v>
+      <c r="E7" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -7180,8 +7236,11 @@
       <c r="D8" s="5">
         <v>0.1</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>300</v>
+      <c r="E8" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F8" s="32" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -7197,8 +7256,11 @@
       <c r="D9" s="5">
         <v>0.1</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>300</v>
+      <c r="E9" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F9" s="32" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -7214,8 +7276,11 @@
       <c r="D10" s="5">
         <v>0.1</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>300</v>
+      <c r="E10" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F10" s="32" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -7231,8 +7296,11 @@
       <c r="D11" s="5">
         <v>0.1</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>300</v>
+      <c r="E11" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F11" s="32" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -7248,8 +7316,11 @@
       <c r="D12" s="5">
         <v>0.1</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>300</v>
+      <c r="E12" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F12" s="32" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -7265,8 +7336,11 @@
       <c r="D13" s="5">
         <v>0.1</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>300</v>
+      <c r="E13" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F13" s="32" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -7282,8 +7356,11 @@
       <c r="D14" s="5">
         <v>0.1</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>300</v>
+      <c r="E14" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F14" s="32" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -7299,8 +7376,11 @@
       <c r="D15" s="5">
         <v>0.1</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>300</v>
+      <c r="E15" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F15" s="32" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -7316,11 +7396,14 @@
       <c r="D16" s="5">
         <v>0.1</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E16" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F16" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>63</v>
       </c>
@@ -7333,11 +7416,14 @@
       <c r="D17" s="5">
         <v>0.1</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E17" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F17" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>65</v>
       </c>
@@ -7350,11 +7436,14 @@
       <c r="D18" s="5">
         <v>0.1</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E18" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F18" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>67</v>
       </c>
@@ -7367,11 +7456,14 @@
       <c r="D19" s="5">
         <v>0.1</v>
       </c>
-      <c r="E19" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E19" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F19" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>69</v>
       </c>
@@ -7384,11 +7476,14 @@
       <c r="D20" s="5">
         <v>0.1</v>
       </c>
-      <c r="E20" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E20" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F20" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>71</v>
       </c>
@@ -7401,11 +7496,14 @@
       <c r="D21" s="5">
         <v>0.1</v>
       </c>
-      <c r="E21" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E21" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F21" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>73</v>
       </c>
@@ -7418,11 +7516,14 @@
       <c r="D22" s="5">
         <v>0.1</v>
       </c>
-      <c r="E22" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E22" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F22" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>189</v>
       </c>
@@ -7435,11 +7536,14 @@
       <c r="D23" s="5">
         <v>0.1</v>
       </c>
-      <c r="E23" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E23" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F23" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>193</v>
       </c>
@@ -7452,11 +7556,14 @@
       <c r="D24" s="5">
         <v>0.1</v>
       </c>
-      <c r="E24" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E24" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F24" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
         <v>195</v>
       </c>
@@ -7469,11 +7576,14 @@
       <c r="D25" s="5">
         <v>0.08</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E25" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F25" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>197</v>
       </c>
@@ -7486,11 +7596,14 @@
       <c r="D26" s="5">
         <v>0.1</v>
       </c>
-      <c r="E26" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E26" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F26" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
         <v>199</v>
       </c>
@@ -7503,11 +7616,14 @@
       <c r="D27" s="5">
         <v>0.08</v>
       </c>
-      <c r="E27" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E27" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F27" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
         <v>75</v>
       </c>
@@ -7520,11 +7636,14 @@
       <c r="D28" s="5">
         <v>0.1</v>
       </c>
-      <c r="E28" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E28" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F28" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>77</v>
       </c>
@@ -7537,11 +7656,14 @@
       <c r="D29" s="5">
         <v>0.1</v>
       </c>
-      <c r="E29" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E29" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F29" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
         <v>79</v>
       </c>
@@ -7554,11 +7676,14 @@
       <c r="D30" s="5">
         <v>0.1</v>
       </c>
-      <c r="E30" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E30" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F30" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>81</v>
       </c>
@@ -7571,11 +7696,14 @@
       <c r="D31" s="5">
         <v>0.1</v>
       </c>
-      <c r="E31" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E31" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F31" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>83</v>
       </c>
@@ -7588,11 +7716,14 @@
       <c r="D32" s="5">
         <v>0.1</v>
       </c>
-      <c r="E32" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E32" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F32" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>85</v>
       </c>
@@ -7605,11 +7736,14 @@
       <c r="D33" s="5">
         <v>0.1</v>
       </c>
-      <c r="E33" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E33" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F33" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
         <v>201</v>
       </c>
@@ -7622,11 +7756,14 @@
       <c r="D34" s="5">
         <v>0.08</v>
       </c>
-      <c r="E34" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E34" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F34" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
         <v>203</v>
       </c>
@@ -7639,11 +7776,14 @@
       <c r="D35" s="5">
         <v>0.1</v>
       </c>
-      <c r="E35" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E35" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F35" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
         <v>205</v>
       </c>
@@ -7656,11 +7796,14 @@
       <c r="D36" s="5">
         <v>0.1</v>
       </c>
-      <c r="E36" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E36" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F36" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
         <v>87</v>
       </c>
@@ -7673,11 +7816,14 @@
       <c r="D37" s="5">
         <v>0.58405200000000002</v>
       </c>
-      <c r="E37" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E37" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F37" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
         <v>87</v>
       </c>
@@ -7685,16 +7831,19 @@
         <v>2</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D38" s="5">
         <v>8.76078E-2</v>
       </c>
-      <c r="E38" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E38" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F38" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
         <v>89</v>
       </c>
@@ -7707,11 +7856,14 @@
       <c r="D39" s="5">
         <v>0.2169336</v>
       </c>
-      <c r="E39" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E39" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F39" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
         <v>89</v>
       </c>
@@ -7719,16 +7871,19 @@
         <v>2</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D40" s="5">
         <v>1.0846679999999999E-2</v>
       </c>
-      <c r="E40" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E40" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F40" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
         <v>91</v>
       </c>
@@ -7741,11 +7896,14 @@
       <c r="D41" s="5">
         <v>0.35543735999999998</v>
       </c>
-      <c r="E41" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E41" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F41" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
         <v>91</v>
       </c>
@@ -7753,16 +7911,19 @@
         <v>2</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D42" s="5">
         <v>5.3315604000000003E-2</v>
       </c>
-      <c r="E42" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E42" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F42" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
         <v>93</v>
       </c>
@@ -7775,11 +7936,14 @@
       <c r="D43" s="5">
         <v>1.3266324</v>
       </c>
-      <c r="E43" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E43" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F43" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
         <v>93</v>
       </c>
@@ -7787,16 +7951,19 @@
         <v>2</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D44" s="5">
         <v>0.19899486</v>
       </c>
-      <c r="E44" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E44" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F44" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
         <v>172</v>
       </c>
@@ -7809,11 +7976,14 @@
       <c r="D45" s="5">
         <v>0.2169336</v>
       </c>
-      <c r="E45" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E45" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F45" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
         <v>172</v>
       </c>
@@ -7821,16 +7991,19 @@
         <v>2</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D46" s="5">
         <v>3.2540039999999999E-2</v>
       </c>
-      <c r="E46" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E46" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F46" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
         <v>174</v>
       </c>
@@ -7843,11 +8016,14 @@
       <c r="D47" s="5">
         <v>0.29202600000000001</v>
       </c>
-      <c r="E47" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E47" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F47" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
         <v>174</v>
       </c>
@@ -7855,16 +8031,19 @@
         <v>2</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D48" s="5">
         <v>11.604691900000001</v>
       </c>
-      <c r="E48" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E48" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F48" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
         <v>176</v>
       </c>
@@ -7877,11 +8056,14 @@
       <c r="D49" s="5">
         <v>0.2169336</v>
       </c>
-      <c r="E49" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E49" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F49" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
         <v>176</v>
       </c>
@@ -7889,16 +8071,19 @@
         <v>2</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D50" s="5">
         <v>3.2540039999999999E-2</v>
       </c>
-      <c r="E50" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E50" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F50" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
         <v>178</v>
       </c>
@@ -7911,11 +8096,14 @@
       <c r="D51" s="5">
         <v>0.29202600000000001</v>
       </c>
-      <c r="E51" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E51" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F51" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
         <v>178</v>
       </c>
@@ -7923,16 +8111,19 @@
         <v>2</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D52" s="5">
         <v>11.604691900000001</v>
       </c>
-      <c r="E52" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E52" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F52" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
         <v>180</v>
       </c>
@@ -7945,11 +8136,14 @@
       <c r="D53" s="5">
         <v>0.53399039999999998</v>
       </c>
-      <c r="E53" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E53" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F53" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
         <v>180</v>
       </c>
@@ -7957,16 +8151,19 @@
         <v>2</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D54" s="5">
         <v>5.2008939999999999</v>
       </c>
-      <c r="E54" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E54" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F54" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
         <v>182</v>
       </c>
@@ -7979,11 +8176,14 @@
       <c r="D55" s="5">
         <v>0.32706911999999999</v>
       </c>
-      <c r="E55" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E55" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F55" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" s="5" t="s">
         <v>182</v>
       </c>
@@ -7991,16 +8191,19 @@
         <v>2</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D56" s="5">
         <v>0.132496368</v>
       </c>
-      <c r="E56" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E56" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F56" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
         <v>184</v>
       </c>
@@ -8013,11 +8216,14 @@
       <c r="D57" s="5">
         <v>0.62827308000000004</v>
       </c>
-      <c r="E57" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E57" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F57" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
         <v>184</v>
       </c>
@@ -8025,16 +8231,19 @@
         <v>2</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D58" s="5">
         <v>9.4240961999999998E-2</v>
       </c>
-      <c r="E58" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E58" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F58" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
         <v>186</v>
       </c>
@@ -8047,11 +8256,14 @@
       <c r="D59" s="5">
         <v>0.3587748</v>
       </c>
-      <c r="E59" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E59" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F59" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
         <v>186</v>
       </c>
@@ -8059,16 +8271,19 @@
         <v>2</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D60" s="5">
         <v>5.3816219999999998E-2</v>
       </c>
-      <c r="E60" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E60" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F60" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" s="5" t="s">
         <v>187</v>
       </c>
@@ -8081,11 +8296,14 @@
       <c r="D61" s="5">
         <v>0.3587748</v>
       </c>
-      <c r="E61" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E61" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F61" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
         <v>187</v>
       </c>
@@ -8093,16 +8311,19 @@
         <v>2</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D62" s="5">
         <v>5.3816219999999998E-2</v>
       </c>
-      <c r="E62" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E62" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F62" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" s="5" t="s">
         <v>95</v>
       </c>
@@ -8115,11 +8336,14 @@
       <c r="D63" s="5">
         <v>0.37546200000000002</v>
       </c>
-      <c r="E63" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E63" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F63" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
         <v>95</v>
       </c>
@@ -8127,16 +8351,19 @@
         <v>2</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D64" s="5">
         <v>30.301739300000001</v>
       </c>
-      <c r="E64" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E64" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F64" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
         <v>97</v>
       </c>
@@ -8149,11 +8376,14 @@
       <c r="D65" s="5">
         <v>0.75092400000000004</v>
       </c>
-      <c r="E65" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E65" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F65" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
         <v>97</v>
       </c>
@@ -8161,16 +8391,19 @@
         <v>2</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D66" s="5">
         <v>0.11263860000000001</v>
       </c>
-      <c r="E66" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E66" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F66" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
         <v>99</v>
       </c>
@@ -8183,11 +8416,14 @@
       <c r="D67" s="5">
         <v>0.75092400000000004</v>
       </c>
-      <c r="E67" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E67" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F67" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
         <v>99</v>
       </c>
@@ -8195,16 +8431,19 @@
         <v>2</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D68" s="5">
         <v>0.11263860000000001</v>
       </c>
-      <c r="E68" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E68" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F68" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
         <v>101</v>
       </c>
@@ -8217,11 +8456,14 @@
       <c r="D69" s="5">
         <v>0.50061599999999995</v>
       </c>
-      <c r="E69" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E69" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F69" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
         <v>101</v>
       </c>
@@ -8229,16 +8471,19 @@
         <v>2</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D70" s="5">
         <v>7.5092400000000004E-2</v>
       </c>
-      <c r="E70" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E70" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F70" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" s="5" t="s">
         <v>103</v>
       </c>
@@ -8251,11 +8496,14 @@
       <c r="D71" s="5">
         <v>0.47180026637745598</v>
       </c>
-      <c r="E71" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E71" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F71" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" s="5" t="s">
         <v>103</v>
       </c>
@@ -8263,16 +8511,19 @@
         <v>2</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D72" s="5">
         <v>7.0770039956618402E-2</v>
       </c>
-      <c r="E72" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E72" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F72" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="5" t="s">
         <v>105</v>
       </c>
@@ -8285,11 +8536,14 @@
       <c r="D73" s="5">
         <v>0.52272095985647904</v>
       </c>
-      <c r="E73" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E73" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F73" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
         <v>105</v>
       </c>
@@ -8297,16 +8551,19 @@
         <v>2</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D74" s="5">
         <v>7.84081439784719E-2</v>
       </c>
-      <c r="E74" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E74" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F74" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
         <v>107</v>
       </c>
@@ -8319,11 +8576,14 @@
       <c r="D75" s="5">
         <v>0.349933385925289</v>
       </c>
-      <c r="E75" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E75" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F75" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
         <v>107</v>
       </c>
@@ -8331,16 +8591,19 @@
         <v>2</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D76" s="5">
         <v>5.2490007888793301E-2</v>
       </c>
-      <c r="E76" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E76" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F76" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
         <v>109</v>
       </c>
@@ -8353,11 +8616,14 @@
       <c r="D77" s="5">
         <v>0.349933385925289</v>
       </c>
-      <c r="E77" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E77" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F77" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
         <v>109</v>
       </c>
@@ -8365,16 +8631,19 @@
         <v>2</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D78" s="5">
         <v>5.2490007888793301E-2</v>
       </c>
-      <c r="E78" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E78" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F78" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
         <v>111</v>
       </c>
@@ -8387,11 +8656,14 @@
       <c r="D79" s="5">
         <v>0.20859</v>
       </c>
-      <c r="E79" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E79" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F79" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
         <v>111</v>
       </c>
@@ -8399,16 +8671,19 @@
         <v>2</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D80" s="5">
         <v>3.1288499999999997E-2</v>
       </c>
-      <c r="E80" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E80" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F80" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
         <v>113</v>
       </c>
@@ -8421,11 +8696,14 @@
       <c r="D81" s="5">
         <v>0.66748799999999997</v>
       </c>
-      <c r="E81" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E81" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F81" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
         <v>113</v>
       </c>
@@ -8433,16 +8711,19 @@
         <v>2</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D82" s="5">
         <v>0.1001232</v>
       </c>
-      <c r="E82" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E82" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F82" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="s">
         <v>115</v>
       </c>
@@ -8455,11 +8736,14 @@
       <c r="D83" s="5">
         <v>0.50759891052905504</v>
       </c>
-      <c r="E83" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E83" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F83" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" s="5" t="s">
         <v>115</v>
       </c>
@@ -8467,16 +8751,19 @@
         <v>2</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D84" s="5">
         <v>7.61398365793583E-2</v>
       </c>
-      <c r="E84" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E84" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F84" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
         <v>117</v>
       </c>
@@ -8489,11 +8776,14 @@
       <c r="D85" s="5">
         <v>0.45</v>
       </c>
-      <c r="E85" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E85" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F85" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" s="5" t="s">
         <v>119</v>
       </c>
@@ -8506,11 +8796,14 @@
       <c r="D86" s="5">
         <v>0.45</v>
       </c>
-      <c r="E86" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E86" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F86" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" s="5" t="s">
         <v>121</v>
       </c>
@@ -8523,11 +8816,14 @@
       <c r="D87" s="5">
         <v>0.32039424</v>
       </c>
-      <c r="E87" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E87" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F87" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" s="5" t="s">
         <v>122</v>
       </c>
@@ -8540,11 +8836,14 @@
       <c r="D88" s="5">
         <v>0.32039424</v>
       </c>
-      <c r="E88" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E88" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F88" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="s">
         <v>124</v>
       </c>
@@ -8557,11 +8856,14 @@
       <c r="D89" s="5">
         <v>0.32039424</v>
       </c>
-      <c r="E89" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E89" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F89" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="s">
         <v>125</v>
       </c>
@@ -8574,11 +8876,14 @@
       <c r="D90" s="5">
         <v>0.32039424</v>
       </c>
-      <c r="E90" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E90" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F90" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" s="5" t="s">
         <v>127</v>
       </c>
@@ -8591,11 +8896,14 @@
       <c r="D91" s="5">
         <v>0.23028335999999999</v>
       </c>
-      <c r="E91" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E91" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F91" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" s="5" t="s">
         <v>129</v>
       </c>
@@ -8608,11 +8916,14 @@
       <c r="D92" s="5">
         <v>0.23028335999999999</v>
       </c>
-      <c r="E92" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E92" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F92" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" s="5" t="s">
         <v>131</v>
       </c>
@@ -8625,11 +8936,14 @@
       <c r="D93" s="5">
         <v>0.26532647999999998</v>
       </c>
-      <c r="E93" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E93" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F93" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" s="5" t="s">
         <v>133</v>
       </c>
@@ -8642,11 +8956,14 @@
       <c r="D94" s="5">
         <v>0.28655259840000002</v>
       </c>
-      <c r="E94" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E94" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F94" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" s="5" t="s">
         <v>135</v>
       </c>
@@ -8659,11 +8976,14 @@
       <c r="D95" s="5">
         <v>0.25951933440000002</v>
       </c>
-      <c r="E95" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E95" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F95" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" s="5" t="s">
         <v>137</v>
       </c>
@@ -8676,11 +8996,14 @@
       <c r="D96" s="5">
         <v>0.29736590400000001</v>
       </c>
-      <c r="E96" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E96" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F96" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" s="5" t="s">
         <v>139</v>
       </c>
@@ -8693,11 +9016,14 @@
       <c r="D97" s="5">
         <v>0.25951933440000002</v>
       </c>
-      <c r="E97" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E97" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F97" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" s="5" t="s">
         <v>141</v>
       </c>
@@ -8710,11 +9036,14 @@
       <c r="D98" s="5">
         <v>0.18022176000000001</v>
       </c>
-      <c r="E98" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E98" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F98" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" s="5" t="s">
         <v>143</v>
       </c>
@@ -8727,11 +9056,14 @@
       <c r="D99" s="5">
         <v>0.3504312</v>
       </c>
-      <c r="E99" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E99" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F99" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" s="5" t="s">
         <v>145</v>
       </c>
@@ -8744,11 +9076,14 @@
       <c r="D100" s="5">
         <v>0.133163856</v>
       </c>
-      <c r="E100" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E100" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F100" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" s="5" t="s">
         <v>147</v>
       </c>
@@ -8761,11 +9096,14 @@
       <c r="D101" s="5">
         <v>0.1752156</v>
       </c>
-      <c r="E101" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E101" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F101" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" s="5" t="s">
         <v>149</v>
       </c>
@@ -8778,11 +9116,14 @@
       <c r="D102" s="5">
         <v>0.32039424</v>
       </c>
-      <c r="E102" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E102" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F102" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" s="5" t="s">
         <v>151</v>
       </c>
@@ -8795,11 +9136,14 @@
       <c r="D103" s="5">
         <v>0.19023408</v>
       </c>
-      <c r="E103" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E103" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F103" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" s="5" t="s">
         <v>153</v>
       </c>
@@ -8812,11 +9156,14 @@
       <c r="D104" s="5">
         <v>0.36795275999999999</v>
       </c>
-      <c r="E104" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E104" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F104" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" s="5" t="s">
         <v>157</v>
       </c>
@@ -8829,11 +9176,14 @@
       <c r="D105" s="5">
         <v>0.81600408000000002</v>
       </c>
-      <c r="E105" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E105" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F105" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" s="5" t="s">
         <v>159</v>
       </c>
@@ -8846,11 +9196,14 @@
       <c r="D106" s="5">
         <v>0.875076768</v>
       </c>
-      <c r="E106" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E106" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F106" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" s="5" t="s">
         <v>161</v>
       </c>
@@ -8863,11 +9216,14 @@
       <c r="D107" s="5">
         <v>0.75342708000000003</v>
       </c>
-      <c r="E107" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E107" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F107" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="5" t="s">
         <v>163</v>
       </c>
@@ -8880,11 +9236,14 @@
       <c r="D108" s="5">
         <v>0.72288950399999996</v>
       </c>
-      <c r="E108" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E108" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F108" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" s="5" t="s">
         <v>164</v>
       </c>
@@ -8897,11 +9256,14 @@
       <c r="D109" s="5">
         <v>0.72288950399999996</v>
       </c>
-      <c r="E109" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E109" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F109" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" s="5" t="s">
         <v>166</v>
       </c>
@@ -8914,11 +9276,14 @@
       <c r="D110" s="5">
         <v>0.46544999999999997</v>
       </c>
-      <c r="E110" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E110" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F110" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="5" t="s">
         <v>166</v>
       </c>
@@ -8926,16 +9291,19 @@
         <v>2</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D111" s="5">
         <v>7.7575000000000005E-2</v>
       </c>
-      <c r="E111" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E111" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F111" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" s="5" t="s">
         <v>168</v>
       </c>
@@ -8948,11 +9316,14 @@
       <c r="D112" s="5">
         <v>2.0562619999999998</v>
       </c>
-      <c r="E112" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E112" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F112" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" s="5" t="s">
         <v>168</v>
       </c>
@@ -8960,16 +9331,19 @@
         <v>2</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D113" s="5">
         <v>0.1028131</v>
       </c>
-      <c r="E113" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E113" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F113" s="32" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" s="5" t="s">
         <v>170</v>
       </c>
@@ -8982,8 +9356,11 @@
       <c r="D114" s="5">
         <v>0.72907211159999996</v>
       </c>
-      <c r="E114" s="5" t="s">
-        <v>300</v>
+      <c r="E114" s="32" t="s">
+        <v>692</v>
+      </c>
+      <c r="F114" s="32" t="s">
+        <v>693</v>
       </c>
     </row>
   </sheetData>
@@ -8994,7 +9371,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:P5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -9007,7 +9384,7 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -9030,79 +9407,79 @@
         <v>32</v>
       </c>
       <c r="B2" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="C2" s="14" t="s">
         <v>303</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="D2" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="E2" s="14" t="s">
         <v>305</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="F2" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="G2" s="14" t="s">
         <v>307</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="H2" s="14" t="s">
         <v>308</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="I2" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="J2" s="14" t="s">
         <v>310</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="K2" s="14" t="s">
         <v>311</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="L2" s="14" t="s">
         <v>312</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="M2" s="14" t="s">
         <v>313</v>
       </c>
-      <c r="M2" s="14" t="s">
+      <c r="N2" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="N2" s="14" t="s">
+      <c r="O2" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="O2" s="14" t="s">
+      <c r="P2" s="14" t="s">
         <v>316</v>
-      </c>
-      <c r="P2" s="14" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:16" s="10" customFormat="1" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
+        <v>317</v>
+      </c>
+      <c r="B3" s="16" t="s">
         <v>318</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="C3" s="16" t="s">
         <v>319</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>320</v>
       </c>
       <c r="D3" s="17"/>
       <c r="E3" s="18" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F3" s="19"/>
       <c r="G3" s="20"/>
       <c r="H3" s="19"/>
       <c r="I3" s="20" t="s">
+        <v>321</v>
+      </c>
+      <c r="J3" s="20" t="s">
         <v>322</v>
-      </c>
-      <c r="J3" s="20" t="s">
-        <v>323</v>
       </c>
       <c r="K3" s="20"/>
       <c r="L3" s="19"/>
       <c r="M3" s="20"/>
       <c r="N3" s="23" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O3" s="15" t="s">
         <v>15</v>
@@ -9113,29 +9490,29 @@
     </row>
     <row r="4" spans="1:16" s="10" customFormat="1" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="21" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B4" s="16" t="s">
+        <v>318</v>
+      </c>
+      <c r="C4" s="16" t="s">
         <v>319</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>320</v>
       </c>
       <c r="D4" s="17"/>
       <c r="E4" s="18" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F4" s="19"/>
       <c r="G4" s="20"/>
       <c r="H4" s="19"/>
       <c r="I4" s="20" t="s">
+        <v>321</v>
+      </c>
+      <c r="J4" s="20" t="s">
         <v>322</v>
       </c>
-      <c r="J4" s="20" t="s">
-        <v>323</v>
-      </c>
       <c r="N4" s="24" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="O4" s="25" t="s">
         <v>40</v>
@@ -9146,29 +9523,29 @@
     </row>
     <row r="5" spans="1:16" s="10" customFormat="1" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="21" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B5" s="16" t="s">
+        <v>318</v>
+      </c>
+      <c r="C5" s="16" t="s">
         <v>319</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>320</v>
       </c>
       <c r="D5" s="17"/>
       <c r="E5" s="18" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F5" s="19"/>
       <c r="G5" s="20"/>
       <c r="H5" s="19"/>
       <c r="I5" s="20" t="s">
+        <v>321</v>
+      </c>
+      <c r="J5" s="20" t="s">
         <v>322</v>
       </c>
-      <c r="J5" s="20" t="s">
-        <v>323</v>
-      </c>
       <c r="N5" s="24" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="O5" s="25" t="s">
         <v>190</v>
@@ -9183,7 +9560,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -9200,7 +9577,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
@@ -9294,7 +9671,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D5" s="7">
         <v>1</v>
@@ -9319,7 +9696,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:J4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -9338,44 +9715,44 @@
   <sheetData>
     <row r="1" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>332</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>333</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>339</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B3" s="7">
         <v>2000</v>
@@ -9384,16 +9761,16 @@
         <v>1</v>
       </c>
       <c r="D3" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="E3" s="9" t="s">
         <v>342</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="F3" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="G3" s="7" t="s">
         <v>344</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>345</v>
       </c>
       <c r="H3" s="7">
         <v>3.1E-2</v>
@@ -9402,12 +9779,12 @@
         <v>0.4</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B4" s="7">
         <v>2000</v>
@@ -9419,13 +9796,13 @@
         <v>22</v>
       </c>
       <c r="E4" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>344</v>
-      </c>
       <c r="G4" s="7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H4" s="7">
         <v>3.6999999999999998E-2</v>
@@ -9434,7 +9811,7 @@
         <v>0.1</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
   </sheetData>
@@ -9447,7 +9824,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:H4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -9463,7 +9840,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
@@ -9471,16 +9848,16 @@
         <v>32</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="8" t="s">
         <v>351</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="8" t="s">
         <v>352</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>353</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>8</v>
@@ -9497,42 +9874,6 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="5"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="12.875" customWidth="1"/>
-    <col min="2" max="2" width="14.625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="7">
-        <v>3100090136</v>
-      </c>
-      <c r="B3" s="7">
-        <v>0.4</v>
-      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="16" type="noConversion"/>
@@ -9863,7 +10204,7 @@
         <v>65</v>
       </c>
       <c r="G18" s="44" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>41</v>
@@ -10709,8 +11050,8 @@
       <c r="C68" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D68" s="5" t="s">
-        <v>163</v>
+      <c r="D68" s="5">
+        <v>3100070021</v>
       </c>
       <c r="G68" s="39" t="s">
         <v>40</v>
@@ -11091,6 +11432,42 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12.875" customWidth="1"/>
+    <col min="2" max="2" width="14.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="7">
+        <v>3100090136</v>
+      </c>
+      <c r="B3" s="7">
+        <v>0.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:G332"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -11105,7 +11482,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
@@ -11116,10 +11493,10 @@
         <v>276</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>358</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>359</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>8</v>
@@ -11139,7 +11516,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -11150,7 +11527,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -11161,7 +11538,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -11172,7 +11549,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -11183,7 +11560,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -11194,7 +11571,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -11205,7 +11582,7 @@
         <v>2</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -11216,7 +11593,7 @@
         <v>3</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -11227,7 +11604,7 @@
         <v>4</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -11238,7 +11615,7 @@
         <v>5</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -11249,7 +11626,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -11260,7 +11637,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -11271,7 +11648,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -11282,7 +11659,7 @@
         <v>4</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -11293,7 +11670,7 @@
         <v>5</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -11304,7 +11681,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -11315,7 +11692,7 @@
         <v>2</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -11326,7 +11703,7 @@
         <v>3</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -11337,7 +11714,7 @@
         <v>4</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -11348,7 +11725,7 @@
         <v>5</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -11359,7 +11736,7 @@
         <v>1</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -11370,7 +11747,7 @@
         <v>2</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -11381,7 +11758,7 @@
         <v>3</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -11392,7 +11769,7 @@
         <v>4</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -11403,7 +11780,7 @@
         <v>5</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -11414,7 +11791,7 @@
         <v>1</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -11425,7 +11802,7 @@
         <v>2</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -11436,7 +11813,7 @@
         <v>3</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
@@ -11447,7 +11824,7 @@
         <v>4</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -11458,7 +11835,7 @@
         <v>5</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -11469,7 +11846,7 @@
         <v>1</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -11480,7 +11857,7 @@
         <v>2</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -11491,7 +11868,7 @@
         <v>3</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
@@ -11502,7 +11879,7 @@
         <v>4</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
@@ -11513,7 +11890,7 @@
         <v>5</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
@@ -11524,7 +11901,7 @@
         <v>1</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
@@ -11535,7 +11912,7 @@
         <v>2</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
@@ -11546,7 +11923,7 @@
         <v>3</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
@@ -11557,7 +11934,7 @@
         <v>4</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
@@ -11568,7 +11945,7 @@
         <v>5</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
@@ -11579,7 +11956,7 @@
         <v>1</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
@@ -11590,7 +11967,7 @@
         <v>2</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
@@ -11601,7 +11978,7 @@
         <v>3</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
@@ -11612,7 +11989,7 @@
         <v>4</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
@@ -11623,7 +12000,7 @@
         <v>5</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
@@ -11634,7 +12011,7 @@
         <v>1</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
@@ -11645,7 +12022,7 @@
         <v>2</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
@@ -11656,7 +12033,7 @@
         <v>3</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
@@ -11667,7 +12044,7 @@
         <v>4</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
@@ -11678,7 +12055,7 @@
         <v>5</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
@@ -11689,7 +12066,7 @@
         <v>1</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
@@ -11700,7 +12077,7 @@
         <v>2</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
@@ -11711,7 +12088,7 @@
         <v>3</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
@@ -11722,7 +12099,7 @@
         <v>4</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
@@ -11733,7 +12110,7 @@
         <v>5</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
@@ -11744,7 +12121,7 @@
         <v>1</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
@@ -11755,7 +12132,7 @@
         <v>2</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
@@ -11766,7 +12143,7 @@
         <v>3</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
@@ -11777,7 +12154,7 @@
         <v>4</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
@@ -11788,7 +12165,7 @@
         <v>5</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
@@ -11799,7 +12176,7 @@
         <v>1</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
@@ -11810,7 +12187,7 @@
         <v>2</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
@@ -11821,7 +12198,7 @@
         <v>3</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
@@ -11832,7 +12209,7 @@
         <v>4</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
@@ -11843,7 +12220,7 @@
         <v>5</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
@@ -11854,7 +12231,7 @@
         <v>1</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
@@ -11865,7 +12242,7 @@
         <v>2</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
@@ -11876,7 +12253,7 @@
         <v>3</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
@@ -11887,7 +12264,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
@@ -11898,7 +12275,7 @@
         <v>5</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
@@ -11909,7 +12286,7 @@
         <v>1</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
@@ -11920,7 +12297,7 @@
         <v>2</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
@@ -11931,7 +12308,7 @@
         <v>3</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
@@ -11942,7 +12319,7 @@
         <v>4</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
@@ -11953,7 +12330,7 @@
         <v>5</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
@@ -11964,7 +12341,7 @@
         <v>1</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
@@ -11975,7 +12352,7 @@
         <v>2</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
@@ -11986,7 +12363,7 @@
         <v>3</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.2">
@@ -11997,7 +12374,7 @@
         <v>4</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.2">
@@ -12008,7 +12385,7 @@
         <v>5</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.2">
@@ -12019,7 +12396,7 @@
         <v>1</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.2">
@@ -12030,7 +12407,7 @@
         <v>2</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.2">
@@ -12041,7 +12418,7 @@
         <v>3</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.2">
@@ -12052,7 +12429,7 @@
         <v>4</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
@@ -12063,7 +12440,7 @@
         <v>5</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
@@ -12074,7 +12451,7 @@
         <v>1</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.2">
@@ -12085,7 +12462,7 @@
         <v>2</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
@@ -12096,7 +12473,7 @@
         <v>3</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.2">
@@ -12107,7 +12484,7 @@
         <v>4</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.2">
@@ -12118,7 +12495,7 @@
         <v>5</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.2">
@@ -12129,7 +12506,7 @@
         <v>1</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.2">
@@ -12140,7 +12517,7 @@
         <v>2</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.2">
@@ -12151,7 +12528,7 @@
         <v>3</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.2">
@@ -12162,7 +12539,7 @@
         <v>4</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.2">
@@ -12173,7 +12550,7 @@
         <v>5</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
@@ -12184,7 +12561,7 @@
         <v>1</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
@@ -12195,7 +12572,7 @@
         <v>2</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.2">
@@ -12206,7 +12583,7 @@
         <v>3</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
@@ -12217,7 +12594,7 @@
         <v>4</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.2">
@@ -12228,7 +12605,7 @@
         <v>5</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.2">
@@ -12239,7 +12616,7 @@
         <v>1</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.2">
@@ -12250,7 +12627,7 @@
         <v>2</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.2">
@@ -12261,7 +12638,7 @@
         <v>3</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.2">
@@ -12272,7 +12649,7 @@
         <v>4</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.2">
@@ -12283,7 +12660,7 @@
         <v>5</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.2">
@@ -12294,7 +12671,7 @@
         <v>1</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.2">
@@ -12305,7 +12682,7 @@
         <v>2</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
@@ -12316,7 +12693,7 @@
         <v>3</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.2">
@@ -12327,7 +12704,7 @@
         <v>4</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
@@ -12338,7 +12715,7 @@
         <v>5</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.2">
@@ -12349,7 +12726,7 @@
         <v>1</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.2">
@@ -12360,7 +12737,7 @@
         <v>2</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.2">
@@ -12371,7 +12748,7 @@
         <v>3</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.2">
@@ -12382,7 +12759,7 @@
         <v>4</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.2">
@@ -12393,7 +12770,7 @@
         <v>5</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.2">
@@ -12404,7 +12781,7 @@
         <v>1</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.2">
@@ -12415,7 +12792,7 @@
         <v>2</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.2">
@@ -12426,7 +12803,7 @@
         <v>3</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
@@ -12437,7 +12814,7 @@
         <v>4</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.2">
@@ -12448,7 +12825,7 @@
         <v>5</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
@@ -12459,7 +12836,7 @@
         <v>1</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.2">
@@ -12470,7 +12847,7 @@
         <v>2</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.2">
@@ -12481,7 +12858,7 @@
         <v>3</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.2">
@@ -12492,7 +12869,7 @@
         <v>4</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.2">
@@ -12503,7 +12880,7 @@
         <v>5</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.2">
@@ -12514,7 +12891,7 @@
         <v>1</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.2">
@@ -12525,7 +12902,7 @@
         <v>2</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.2">
@@ -12536,7 +12913,7 @@
         <v>3</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.2">
@@ -12547,7 +12924,7 @@
         <v>4</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
@@ -12558,7 +12935,7 @@
         <v>5</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.2">
@@ -12569,7 +12946,7 @@
         <v>1</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
@@ -12580,7 +12957,7 @@
         <v>2</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.2">
@@ -12591,7 +12968,7 @@
         <v>3</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.2">
@@ -12602,7 +12979,7 @@
         <v>4</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.2">
@@ -12613,7 +12990,7 @@
         <v>5</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.2">
@@ -12624,7 +13001,7 @@
         <v>1</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.2">
@@ -12635,7 +13012,7 @@
         <v>2</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.2">
@@ -12646,7 +13023,7 @@
         <v>3</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.2">
@@ -12657,7 +13034,7 @@
         <v>4</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.2">
@@ -12668,7 +13045,7 @@
         <v>5</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
@@ -12679,7 +13056,7 @@
         <v>1</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.2">
@@ -12690,7 +13067,7 @@
         <v>2</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
@@ -12701,7 +13078,7 @@
         <v>3</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.2">
@@ -12712,7 +13089,7 @@
         <v>4</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.2">
@@ -12723,7 +13100,7 @@
         <v>5</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.2">
@@ -12734,7 +13111,7 @@
         <v>1</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.2">
@@ -12745,7 +13122,7 @@
         <v>2</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.2">
@@ -12756,7 +13133,7 @@
         <v>3</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.2">
@@ -12767,7 +13144,7 @@
         <v>4</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.2">
@@ -12778,7 +13155,7 @@
         <v>5</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.2">
@@ -12789,7 +13166,7 @@
         <v>1</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
@@ -12800,7 +13177,7 @@
         <v>2</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.2">
@@ -12811,7 +13188,7 @@
         <v>3</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
@@ -12822,7 +13199,7 @@
         <v>4</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.2">
@@ -12833,7 +13210,7 @@
         <v>5</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.2">
@@ -12844,7 +13221,7 @@
         <v>1</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.2">
@@ -12855,7 +13232,7 @@
         <v>2</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.2">
@@ -12866,7 +13243,7 @@
         <v>3</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.2">
@@ -12877,7 +13254,7 @@
         <v>4</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.2">
@@ -12888,7 +13265,7 @@
         <v>5</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.2">
@@ -12899,7 +13276,7 @@
         <v>1</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.2">
@@ -12910,7 +13287,7 @@
         <v>2</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
@@ -12921,7 +13298,7 @@
         <v>3</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.2">
@@ -12932,7 +13309,7 @@
         <v>4</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
@@ -12943,7 +13320,7 @@
         <v>5</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.2">
@@ -12954,7 +13331,7 @@
         <v>1</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.2">
@@ -12965,7 +13342,7 @@
         <v>2</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.2">
@@ -12976,7 +13353,7 @@
         <v>3</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.2">
@@ -12987,7 +13364,7 @@
         <v>4</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.2">
@@ -12998,7 +13375,7 @@
         <v>5</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.2">
@@ -13009,7 +13386,7 @@
         <v>1</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.2">
@@ -13020,7 +13397,7 @@
         <v>2</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.2">
@@ -13031,7 +13408,7 @@
         <v>3</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
@@ -13042,7 +13419,7 @@
         <v>4</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.2">
@@ -13053,7 +13430,7 @@
         <v>5</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
@@ -13064,7 +13441,7 @@
         <v>1</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.2">
@@ -13075,7 +13452,7 @@
         <v>2</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.2">
@@ -13086,7 +13463,7 @@
         <v>3</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.2">
@@ -13097,7 +13474,7 @@
         <v>4</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.2">
@@ -13108,7 +13485,7 @@
         <v>5</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.2">
@@ -13119,7 +13496,7 @@
         <v>1</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.2">
@@ -13130,7 +13507,7 @@
         <v>2</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.2">
@@ -13141,7 +13518,7 @@
         <v>3</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.2">
@@ -13152,7 +13529,7 @@
         <v>4</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
@@ -13163,7 +13540,7 @@
         <v>5</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.2">
@@ -13174,7 +13551,7 @@
         <v>1</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
@@ -13185,7 +13562,7 @@
         <v>2</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.2">
@@ -13196,7 +13573,7 @@
         <v>3</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.2">
@@ -13207,7 +13584,7 @@
         <v>4</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.2">
@@ -13218,7 +13595,7 @@
         <v>5</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.2">
@@ -13229,7 +13606,7 @@
         <v>1</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.2">
@@ -13240,7 +13617,7 @@
         <v>2</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.2">
@@ -13251,7 +13628,7 @@
         <v>3</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.2">
@@ -13262,7 +13639,7 @@
         <v>4</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.2">
@@ -13273,7 +13650,7 @@
         <v>5</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.2">
@@ -13284,7 +13661,7 @@
         <v>1</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.2">
@@ -13295,7 +13672,7 @@
         <v>2</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
@@ -13306,7 +13683,7 @@
         <v>3</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.2">
@@ -13317,7 +13694,7 @@
         <v>4</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.2">
@@ -13328,7 +13705,7 @@
         <v>5</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.2">
@@ -13339,7 +13716,7 @@
         <v>1</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.2">
@@ -13350,7 +13727,7 @@
         <v>2</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.2">
@@ -13361,7 +13738,7 @@
         <v>3</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.2">
@@ -13372,7 +13749,7 @@
         <v>4</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.2">
@@ -13383,7 +13760,7 @@
         <v>5</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.2">
@@ -13394,7 +13771,7 @@
         <v>1</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
@@ -13405,7 +13782,7 @@
         <v>2</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.2">
@@ -13416,7 +13793,7 @@
         <v>3</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
@@ -13427,7 +13804,7 @@
         <v>4</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.2">
@@ -13438,7 +13815,7 @@
         <v>5</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.2">
@@ -13449,7 +13826,7 @@
         <v>1</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.2">
@@ -13460,7 +13837,7 @@
         <v>2</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.2">
@@ -13471,7 +13848,7 @@
         <v>3</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.2">
@@ -13482,7 +13859,7 @@
         <v>4</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.2">
@@ -13493,7 +13870,7 @@
         <v>5</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.2">
@@ -13504,7 +13881,7 @@
         <v>1</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.2">
@@ -13515,7 +13892,7 @@
         <v>2</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
@@ -13526,7 +13903,7 @@
         <v>3</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.2">
@@ -13537,7 +13914,7 @@
         <v>4</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
@@ -13548,7 +13925,7 @@
         <v>5</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.2">
@@ -13559,7 +13936,7 @@
         <v>1</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.2">
@@ -13570,7 +13947,7 @@
         <v>2</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.2">
@@ -13581,7 +13958,7 @@
         <v>3</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.2">
@@ -13592,7 +13969,7 @@
         <v>4</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.2">
@@ -13603,7 +13980,7 @@
         <v>5</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.2">
@@ -13614,7 +13991,7 @@
         <v>1</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.2">
@@ -13625,7 +14002,7 @@
         <v>2</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.2">
@@ -13636,7 +14013,7 @@
         <v>3</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.2">
@@ -13647,7 +14024,7 @@
         <v>4</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.2">
@@ -13658,7 +14035,7 @@
         <v>5</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
@@ -13669,7 +14046,7 @@
         <v>1</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.2">
@@ -13680,7 +14057,7 @@
         <v>2</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.2">
@@ -13691,7 +14068,7 @@
         <v>3</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.2">
@@ -13702,7 +14079,7 @@
         <v>4</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.2">
@@ -13713,7 +14090,7 @@
         <v>5</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.2">
@@ -13724,7 +14101,7 @@
         <v>1</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.2">
@@ -13735,7 +14112,7 @@
         <v>2</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.2">
@@ -13746,7 +14123,7 @@
         <v>3</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.2">
@@ -13757,7 +14134,7 @@
         <v>4</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.2">
@@ -13768,7 +14145,7 @@
         <v>5</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.2">
@@ -13779,7 +14156,7 @@
         <v>1</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
@@ -13790,7 +14167,7 @@
         <v>2</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.2">
@@ -13801,7 +14178,7 @@
         <v>3</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.2">
@@ -13812,7 +14189,7 @@
         <v>4</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.2">
@@ -13823,7 +14200,7 @@
         <v>5</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.2">
@@ -13834,7 +14211,7 @@
         <v>1</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.2">
@@ -13845,7 +14222,7 @@
         <v>2</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.2">
@@ -13856,7 +14233,7 @@
         <v>3</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.2">
@@ -13867,7 +14244,7 @@
         <v>4</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.2">
@@ -13878,7 +14255,7 @@
         <v>5</v>
       </c>
       <c r="C252" s="5" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.2">
@@ -13889,7 +14266,7 @@
         <v>1</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.2">
@@ -13900,7 +14277,7 @@
         <v>2</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
@@ -13911,7 +14288,7 @@
         <v>3</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.2">
@@ -13922,7 +14299,7 @@
         <v>4</v>
       </c>
       <c r="C256" s="5" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.2">
@@ -13933,7 +14310,7 @@
         <v>5</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.2">
@@ -13944,7 +14321,7 @@
         <v>1</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.2">
@@ -13955,7 +14332,7 @@
         <v>2</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.2">
@@ -13966,7 +14343,7 @@
         <v>3</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.2">
@@ -13977,7 +14354,7 @@
         <v>4</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.2">
@@ -13988,7 +14365,7 @@
         <v>5</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.2">
@@ -13999,7 +14376,7 @@
         <v>1</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.2">
@@ -14010,7 +14387,7 @@
         <v>2</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.2">
@@ -14021,7 +14398,7 @@
         <v>3</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
@@ -14032,7 +14409,7 @@
         <v>4</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.2">
@@ -14043,7 +14420,7 @@
         <v>5</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.2">
@@ -14054,7 +14431,7 @@
         <v>1</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.2">
@@ -14065,7 +14442,7 @@
         <v>2</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.2">
@@ -14076,7 +14453,7 @@
         <v>3</v>
       </c>
       <c r="C270" s="5" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.2">
@@ -14087,7 +14464,7 @@
         <v>4</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.2">
@@ -14098,7 +14475,7 @@
         <v>5</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.2">
@@ -14109,7 +14486,7 @@
         <v>1</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.2">
@@ -14120,7 +14497,7 @@
         <v>2</v>
       </c>
       <c r="C274" s="5" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.2">
@@ -14131,7 +14508,7 @@
         <v>3</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.2">
@@ -14142,7 +14519,7 @@
         <v>4</v>
       </c>
       <c r="C276" s="5" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
@@ -14153,7 +14530,7 @@
         <v>5</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.2">
@@ -14164,7 +14541,7 @@
         <v>1</v>
       </c>
       <c r="C278" s="5" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.2">
@@ -14175,7 +14552,7 @@
         <v>2</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.2">
@@ -14186,7 +14563,7 @@
         <v>3</v>
       </c>
       <c r="C280" s="5" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.2">
@@ -14197,7 +14574,7 @@
         <v>4</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.2">
@@ -14208,7 +14585,7 @@
         <v>5</v>
       </c>
       <c r="C282" s="5" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.2">
@@ -14219,7 +14596,7 @@
         <v>1</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.2">
@@ -14230,7 +14607,7 @@
         <v>2</v>
       </c>
       <c r="C284" s="5" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.2">
@@ -14241,7 +14618,7 @@
         <v>3</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.2">
@@ -14252,7 +14629,7 @@
         <v>4</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.2">
@@ -14263,7 +14640,7 @@
         <v>5</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
@@ -14274,7 +14651,7 @@
         <v>1</v>
       </c>
       <c r="C288" s="5" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.2">
@@ -14285,7 +14662,7 @@
         <v>2</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.2">
@@ -14296,7 +14673,7 @@
         <v>3</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.2">
@@ -14307,7 +14684,7 @@
         <v>4</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.2">
@@ -14318,7 +14695,7 @@
         <v>5</v>
       </c>
       <c r="C292" s="5" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.2">
@@ -14329,7 +14706,7 @@
         <v>1</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.2">
@@ -14340,7 +14717,7 @@
         <v>2</v>
       </c>
       <c r="C294" s="5" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.2">
@@ -14351,7 +14728,7 @@
         <v>3</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.2">
@@ -14362,7 +14739,7 @@
         <v>4</v>
       </c>
       <c r="C296" s="5" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
@@ -14373,7 +14750,7 @@
         <v>5</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.2">
@@ -14384,7 +14761,7 @@
         <v>1</v>
       </c>
       <c r="C298" s="5" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
@@ -14395,7 +14772,7 @@
         <v>2</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.2">
@@ -14406,7 +14783,7 @@
         <v>3</v>
       </c>
       <c r="C300" s="5" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.2">
@@ -14417,7 +14794,7 @@
         <v>4</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.2">
@@ -14428,7 +14805,7 @@
         <v>5</v>
       </c>
       <c r="C302" s="5" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.2">
@@ -14439,7 +14816,7 @@
         <v>1</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.2">
@@ -14450,7 +14827,7 @@
         <v>2</v>
       </c>
       <c r="C304" s="5" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.2">
@@ -14461,7 +14838,7 @@
         <v>3</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.2">
@@ -14472,7 +14849,7 @@
         <v>4</v>
       </c>
       <c r="C306" s="5" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.2">
@@ -14483,7 +14860,7 @@
         <v>5</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.2">
@@ -14494,7 +14871,7 @@
         <v>1</v>
       </c>
       <c r="C308" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.2">
@@ -14505,7 +14882,7 @@
         <v>2</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
@@ -14516,7 +14893,7 @@
         <v>3</v>
       </c>
       <c r="C310" s="5" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.2">
@@ -14527,7 +14904,7 @@
         <v>4</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.2">
@@ -14538,7 +14915,7 @@
         <v>5</v>
       </c>
       <c r="C312" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.2">
@@ -14549,7 +14926,7 @@
         <v>1</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.2">
@@ -14560,7 +14937,7 @@
         <v>2</v>
       </c>
       <c r="C314" s="5" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.2">
@@ -14571,7 +14948,7 @@
         <v>3</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.2">
@@ -14582,7 +14959,7 @@
         <v>4</v>
       </c>
       <c r="C316" s="5" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.2">
@@ -14593,7 +14970,7 @@
         <v>5</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.2">
@@ -14604,7 +14981,7 @@
         <v>1</v>
       </c>
       <c r="C318" s="5" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.2">
@@ -14615,7 +14992,7 @@
         <v>2</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.2">
@@ -14626,7 +15003,7 @@
         <v>3</v>
       </c>
       <c r="C320" s="5" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
@@ -14637,7 +15014,7 @@
         <v>4</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.2">
@@ -14648,7 +15025,7 @@
         <v>5</v>
       </c>
       <c r="C322" s="5" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.2">
@@ -14659,7 +15036,7 @@
         <v>1</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.2">
@@ -14670,7 +15047,7 @@
         <v>2</v>
       </c>
       <c r="C324" s="5" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.2">
@@ -14681,7 +15058,7 @@
         <v>3</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.2">
@@ -14692,7 +15069,7 @@
         <v>4</v>
       </c>
       <c r="C326" s="5" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.2">
@@ -14703,7 +15080,7 @@
         <v>5</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.2">
@@ -14714,7 +15091,7 @@
         <v>1</v>
       </c>
       <c r="C328" s="5" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.2">
@@ -14725,7 +15102,7 @@
         <v>2</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.2">
@@ -14736,7 +15113,7 @@
         <v>3</v>
       </c>
       <c r="C330" s="5" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.2">
@@ -14747,7 +15124,7 @@
         <v>4</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
@@ -14758,7 +15135,7 @@
         <v>5</v>
       </c>
       <c r="C332" s="5" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
   </sheetData>
@@ -14822,7 +15199,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="43" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -15638,6 +16015,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K141"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -15689,9 +16067,9 @@
         <v>240</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
-        <v>62</v>
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="5">
+        <v>3100210010</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>220</v>
@@ -15712,7 +16090,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>62</v>
       </c>
@@ -15735,7 +16113,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>62</v>
       </c>
@@ -15758,7 +16136,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>62</v>
       </c>
@@ -15781,7 +16159,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>42</v>
       </c>
@@ -15804,7 +16182,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>42</v>
       </c>
@@ -15827,7 +16205,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>42</v>
       </c>
@@ -15850,7 +16228,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>42</v>
       </c>
@@ -15873,7 +16251,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>189</v>
       </c>
@@ -15896,7 +16274,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>189</v>
       </c>
@@ -15919,7 +16297,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>189</v>
       </c>
@@ -15942,7 +16320,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>189</v>
       </c>
@@ -15965,7 +16343,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>193</v>
       </c>
@@ -15988,7 +16366,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>193</v>
       </c>
@@ -16011,7 +16389,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>193</v>
       </c>
@@ -16034,7 +16412,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>193</v>
       </c>
@@ -16057,7 +16435,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>197</v>
       </c>
@@ -16080,7 +16458,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>197</v>
       </c>
@@ -16103,7 +16481,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>197</v>
       </c>
@@ -16126,7 +16504,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>197</v>
       </c>
@@ -16149,7 +16527,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>195</v>
       </c>
@@ -16172,7 +16550,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>195</v>
       </c>
@@ -16195,7 +16573,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>195</v>
       </c>
@@ -16218,7 +16596,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
         <v>195</v>
       </c>
@@ -16241,7 +16619,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>199</v>
       </c>
@@ -16264,7 +16642,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
         <v>199</v>
       </c>
@@ -16287,7 +16665,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
         <v>199</v>
       </c>
@@ -16310,7 +16688,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>199</v>
       </c>
@@ -16333,7 +16711,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
         <v>205</v>
       </c>
@@ -16356,7 +16734,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>205</v>
       </c>
@@ -16379,7 +16757,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>205</v>
       </c>
@@ -16402,7 +16780,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>205</v>
       </c>
@@ -16425,7 +16803,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
         <v>201</v>
       </c>
@@ -16448,7 +16826,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
         <v>201</v>
       </c>
@@ -16471,7 +16849,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
         <v>201</v>
       </c>
@@ -16494,7 +16872,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
         <v>201</v>
       </c>
@@ -16517,7 +16895,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
         <v>203</v>
       </c>
@@ -16540,7 +16918,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
         <v>203</v>
       </c>
@@ -16563,7 +16941,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
         <v>203</v>
       </c>
@@ -16586,7 +16964,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
         <v>203</v>
       </c>
@@ -16609,7 +16987,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
         <v>67</v>
       </c>
@@ -16632,7 +17010,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
         <v>67</v>
       </c>
@@ -16655,7 +17033,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
         <v>50</v>
       </c>
@@ -16678,7 +17056,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
         <v>50</v>
       </c>
@@ -16701,7 +17079,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
         <v>50</v>
       </c>
@@ -16724,7 +17102,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
         <v>50</v>
       </c>
@@ -16747,7 +17125,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
         <v>47</v>
       </c>
@@ -16770,7 +17148,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
         <v>47</v>
       </c>
@@ -16793,7 +17171,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
         <v>47</v>
       </c>
@@ -16816,7 +17194,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
         <v>47</v>
       </c>
@@ -16839,7 +17217,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
         <v>39</v>
       </c>
@@ -16862,7 +17240,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
         <v>39</v>
       </c>
@@ -16885,7 +17263,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
         <v>39</v>
       </c>
@@ -16908,7 +17286,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
         <v>39</v>
       </c>
@@ -16931,7 +17309,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="5" t="s">
         <v>44</v>
       </c>
@@ -16954,7 +17332,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
         <v>44</v>
       </c>
@@ -16977,7 +17355,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
         <v>44</v>
       </c>
@@ -17000,7 +17378,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
         <v>44</v>
       </c>
@@ -17023,7 +17401,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
         <v>54</v>
       </c>
@@ -17046,7 +17424,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" s="5" t="s">
         <v>54</v>
       </c>
@@ -17069,7 +17447,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
         <v>54</v>
       </c>
@@ -17092,7 +17470,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" s="5" t="s">
         <v>54</v>
       </c>
@@ -17115,7 +17493,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
         <v>58</v>
       </c>
@@ -17138,7 +17516,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
         <v>58</v>
       </c>
@@ -17161,7 +17539,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
         <v>58</v>
       </c>
@@ -17184,7 +17562,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
         <v>58</v>
       </c>
@@ -17207,7 +17585,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
         <v>69</v>
       </c>
@@ -17230,7 +17608,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
         <v>69</v>
       </c>
@@ -17253,7 +17631,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
         <v>71</v>
       </c>
@@ -17276,7 +17654,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" s="5" t="s">
         <v>71</v>
       </c>
@@ -17299,7 +17677,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" s="5" t="s">
         <v>73</v>
       </c>
@@ -17322,7 +17700,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" s="5" t="s">
         <v>73</v>
       </c>
@@ -17345,7 +17723,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
         <v>81</v>
       </c>
@@ -17368,7 +17746,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
         <v>81</v>
       </c>
@@ -17391,7 +17769,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
         <v>81</v>
       </c>
@@ -17414,7 +17792,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
         <v>81</v>
       </c>
@@ -17437,7 +17815,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
         <v>79</v>
       </c>
@@ -17460,7 +17838,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
         <v>79</v>
       </c>
@@ -17483,7 +17861,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
         <v>79</v>
       </c>
@@ -17506,7 +17884,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
         <v>79</v>
       </c>
@@ -17529,7 +17907,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
         <v>77</v>
       </c>
@@ -17552,7 +17930,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="s">
         <v>77</v>
       </c>
@@ -17575,7 +17953,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" s="5" t="s">
         <v>77</v>
       </c>
@@ -17598,7 +17976,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
         <v>77</v>
       </c>
@@ -17621,7 +17999,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" s="5" t="s">
         <v>75</v>
       </c>
@@ -17644,7 +18022,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" s="5" t="s">
         <v>75</v>
       </c>
@@ -17667,7 +18045,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" s="5" t="s">
         <v>75</v>
       </c>
@@ -17690,7 +18068,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="s">
         <v>75</v>
       </c>
@@ -17713,7 +18091,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="s">
         <v>60</v>
       </c>
@@ -17736,7 +18114,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" s="5" t="s">
         <v>60</v>
       </c>
@@ -17759,7 +18137,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" s="5" t="s">
         <v>60</v>
       </c>
@@ -17782,7 +18160,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" s="5" t="s">
         <v>60</v>
       </c>
@@ -17805,7 +18183,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" s="5" t="s">
         <v>65</v>
       </c>
@@ -17828,7 +18206,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" s="5" t="s">
         <v>65</v>
       </c>
@@ -17851,7 +18229,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" s="5" t="s">
         <v>65</v>
       </c>
@@ -17874,7 +18252,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" s="5" t="s">
         <v>65</v>
       </c>
@@ -17897,7 +18275,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" s="5" t="s">
         <v>83</v>
       </c>
@@ -17920,7 +18298,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" s="5" t="s">
         <v>83</v>
       </c>
@@ -17943,7 +18321,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" s="5" t="s">
         <v>83</v>
       </c>
@@ -17966,7 +18344,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" s="5" t="s">
         <v>83</v>
       </c>
@@ -17989,7 +18367,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" s="5" t="s">
         <v>85</v>
       </c>
@@ -18012,7 +18390,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" s="5" t="s">
         <v>85</v>
       </c>
@@ -18035,7 +18413,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" s="5" t="s">
         <v>85</v>
       </c>
@@ -18058,7 +18436,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" s="5" t="s">
         <v>85</v>
       </c>
@@ -18081,7 +18459,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" s="5" t="s">
         <v>63</v>
       </c>
@@ -18104,7 +18482,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" s="5" t="s">
         <v>63</v>
       </c>
@@ -18127,7 +18505,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" s="5" t="s">
         <v>63</v>
       </c>
@@ -18150,7 +18528,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" s="5" t="s">
         <v>63</v>
       </c>
@@ -18173,7 +18551,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" s="5" t="s">
         <v>119</v>
       </c>
@@ -18196,7 +18574,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" s="5" t="s">
         <v>119</v>
       </c>
@@ -18219,7 +18597,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" s="5" t="s">
         <v>119</v>
       </c>
@@ -18242,7 +18620,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" s="5" t="s">
         <v>119</v>
       </c>
@@ -18357,7 +18735,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" s="5" t="s">
         <v>48</v>
       </c>
@@ -18380,7 +18758,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" s="5" t="s">
         <v>48</v>
       </c>
@@ -18403,7 +18781,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" s="5" t="s">
         <v>48</v>
       </c>
@@ -18426,7 +18804,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" s="5" t="s">
         <v>48</v>
       </c>
@@ -18449,7 +18827,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" s="5" t="s">
         <v>51</v>
       </c>
@@ -18472,7 +18850,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
         <v>51</v>
       </c>
@@ -18495,7 +18873,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" s="5" t="s">
         <v>51</v>
       </c>
@@ -18518,7 +18896,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" s="5" t="s">
         <v>51</v>
       </c>
@@ -18541,7 +18919,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" s="5" t="s">
         <v>52</v>
       </c>
@@ -18564,7 +18942,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" s="5" t="s">
         <v>52</v>
       </c>
@@ -18587,7 +18965,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" s="5" t="s">
         <v>52</v>
       </c>
@@ -18610,7 +18988,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" s="5" t="s">
         <v>52</v>
       </c>
@@ -18633,7 +19011,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" s="5" t="s">
         <v>46</v>
       </c>
@@ -18656,7 +19034,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" s="5" t="s">
         <v>46</v>
       </c>
@@ -18679,7 +19057,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" s="5" t="s">
         <v>46</v>
       </c>
@@ -18702,7 +19080,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" s="5" t="s">
         <v>46</v>
       </c>
@@ -18725,7 +19103,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" s="5" t="s">
         <v>55</v>
       </c>
@@ -18748,7 +19126,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" s="5" t="s">
         <v>55</v>
       </c>
@@ -18771,7 +19149,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" s="5" t="s">
         <v>55</v>
       </c>
@@ -18794,7 +19172,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" s="5" t="s">
         <v>55</v>
       </c>
@@ -18817,7 +19195,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" s="5" t="s">
         <v>57</v>
       </c>
@@ -18840,7 +19218,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" s="5" t="s">
         <v>57</v>
       </c>
@@ -18863,7 +19241,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140" s="5" t="s">
         <v>57</v>
       </c>
@@ -18886,7 +19264,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" s="5" t="s">
         <v>57</v>
       </c>
@@ -18910,7 +19288,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K141" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:K141" xr:uid="{00000000-0009-0000-0000-000003000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="3120015693"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="150" verticalDpi="150"/>
@@ -21769,7 +22153,7 @@
         <v>262</v>
       </c>
       <c r="E121" s="5">
-        <v>1.6867421760000001</v>
+        <v>12</v>
       </c>
       <c r="F121" s="5" t="s">
         <v>38</v>
@@ -21782,8 +22166,8 @@
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A122" s="5" t="s">
-        <v>163</v>
+      <c r="A122" s="5">
+        <v>3100070021</v>
       </c>
       <c r="B122" s="5">
         <v>3</v>
@@ -21792,7 +22176,7 @@
         <v>264</v>
       </c>
       <c r="E122" s="5">
-        <v>5.8405199999999997E-2</v>
+        <v>15</v>
       </c>
       <c r="F122" s="5" t="s">
         <v>38</v>
